--- a/input data/init_calib_in.xlsx
+++ b/input data/init_calib_in.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\input data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78969AF-5A5C-427B-8117-D038E0989AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7E19C3-165D-4E19-A126-1468B0F9A54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="init_conds" sheetId="1" r:id="rId1"/>
@@ -173,20 +173,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -198,10 +219,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,77 +594,77 @@
       <c r="B2">
         <v>1980</v>
       </c>
-      <c r="C2" s="3">
-        <v>9.2425124802268856E-3</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.8038674482371383E-2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3.6495531028323064E-2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>5.9567355936056086E-3</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1.1168804122244039E-2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>2.6807024534568558E-2</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1.4491792172299102E-3</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1.7358710745963473E-3</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1.4554123423360262E-3</v>
-      </c>
-      <c r="L2" s="3">
-        <v>9.321773380429984E-4</v>
-      </c>
-      <c r="M2" s="3">
-        <v>1.1248839643662324E-3</v>
-      </c>
-      <c r="N2" s="3">
-        <v>9.3127682261217671E-4</v>
-      </c>
-      <c r="O2" s="3">
-        <v>3.7910533017657755E-3</v>
-      </c>
-      <c r="P2" s="3">
-        <v>4.5410392935162818E-3</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>3.8073591590627293E-3</v>
-      </c>
-      <c r="R2" s="3">
-        <v>2.4385762183190955E-3</v>
-      </c>
-      <c r="S2" s="3">
-        <v>2.9426968152120726E-3</v>
-      </c>
-      <c r="T2" s="3">
-        <v>2.4362204696603252E-3</v>
-      </c>
-      <c r="U2" s="3">
-        <v>3.8475143461624624E-2</v>
-      </c>
-      <c r="V2" s="3">
-        <v>4.6086700548772216E-2</v>
-      </c>
-      <c r="W2" s="3">
-        <v>3.864063050409719E-2</v>
-      </c>
-      <c r="X2" s="3">
-        <v>2.4748945048657631E-2</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>2.9865230878345892E-2</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>2.472503671490682E-2</v>
+      <c r="C2" s="6">
+        <v>1.504173599723199E-2</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2.9357058471310291E-2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>5.9394687751976739E-2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>9.6942951817503044E-3</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1.8176681218554019E-2</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4.3627118360180198E-2</v>
+      </c>
+      <c r="I2" s="6">
+        <v>2.358468137844755E-3</v>
+      </c>
+      <c r="J2" s="6">
+        <v>2.8250450821862118E-3</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2.368612243409611E-3</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1.517072922697429E-3</v>
+      </c>
+      <c r="M2" s="6">
+        <v>1.8306935106352409E-3</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1.5156073779766801E-3</v>
+      </c>
+      <c r="O2" s="6">
+        <v>6.169753412677636E-3</v>
+      </c>
+      <c r="P2" s="6">
+        <v>7.39031885023238E-3</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>6.1962903961216963E-3</v>
+      </c>
+      <c r="R2" s="6">
+        <v>3.9686632572644102E-3</v>
+      </c>
+      <c r="S2" s="6">
+        <v>4.7890948169137656E-3</v>
+      </c>
+      <c r="T2" s="6">
+        <v>3.964829391800137E-3</v>
+      </c>
+      <c r="U2" s="6">
+        <v>6.2616409947349877E-2</v>
+      </c>
+      <c r="V2" s="6">
+        <v>7.5003845991139101E-2</v>
+      </c>
+      <c r="W2" s="6">
+        <v>6.288573199686405E-2</v>
+      </c>
+      <c r="X2" s="6">
+        <v>4.0277694883109477E-2</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>4.8604199272602143E-2</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>4.0238785241907167E-2</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
@@ -733,76 +754,76 @@
       <c r="B4">
         <v>1980</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>0.01</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>0.13</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>0.01</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>0.13</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>0.01</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>0.13</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>0.01</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="3">
         <v>0.13</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="3">
         <v>0.01</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="3">
         <v>0.13</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4" s="3">
         <v>0.01</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <v>0.13</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <v>0.01</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="3">
         <v>0.13</v>
       </c>
-      <c r="X4" s="4">
+      <c r="X4" s="3">
         <v>0.01</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="Y4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4" s="3">
         <v>0.13</v>
       </c>
     </row>
@@ -813,76 +834,76 @@
       <c r="B5">
         <v>1980</v>
       </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="O5" s="5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5">
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="X5" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="5">
+      <c r="X5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
@@ -893,76 +914,76 @@
       <c r="B6">
         <v>1980</v>
       </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="O6" s="5">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5">
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="W6" s="5">
+      <c r="W6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="X6" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="5">
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
         <v>1.5E-3</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
@@ -981,7 +1002,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>0.5</v>
       </c>
       <c r="F7" s="1">
@@ -992,7 +1013,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>0.5</v>
       </c>
       <c r="I7" s="1">
@@ -1003,7 +1024,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>0.5</v>
       </c>
       <c r="L7" s="1">
@@ -1014,7 +1035,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <v>0.5</v>
       </c>
       <c r="O7" s="1">
@@ -1025,7 +1046,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
         <v>0.5</v>
       </c>
       <c r="R7" s="1">
@@ -1036,7 +1057,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="4">
         <v>0.5</v>
       </c>
       <c r="U7" s="1">
@@ -1047,7 +1068,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="4">
         <v>0.5</v>
       </c>
       <c r="X7" s="1">
@@ -1058,7 +1079,7 @@
         <f>25/32</f>
         <v>0.78125</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -1173,76 +1194,76 @@
       <c r="B9">
         <v>1980</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>0.3</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>0.3</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>0.3</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>0.3</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>0.3</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>0.3</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>0.15</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>0.15</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>0.15</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>0.15</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="3">
         <v>0.15</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="3">
         <v>0.15</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="3">
         <v>0.15</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="3">
         <v>0.15</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="3">
         <v>0.15</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="3">
         <v>0.15</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="3">
         <v>0.15</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="3">
         <v>0.15</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <v>0.5</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <v>0.5</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="3">
         <v>0.5</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="3">
         <v>0.5</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="3">
         <v>0.5</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="Z9" s="3">
         <v>0.5</v>
       </c>
     </row>
@@ -1347,77 +1368,77 @@
       <c r="B2">
         <v>1980</v>
       </c>
-      <c r="C2" s="3">
-        <v>9.2425124802268856E-3</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.8038674482371383E-2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3.6495531028323064E-2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>5.9567355936056086E-3</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1.1168804122244039E-2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>2.6807024534568558E-2</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1.4491792172299102E-3</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1.7358710745963473E-3</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1.4554123423360262E-3</v>
-      </c>
-      <c r="L2" s="3">
-        <v>9.321773380429984E-4</v>
-      </c>
-      <c r="M2" s="3">
-        <v>1.1248839643662324E-3</v>
-      </c>
-      <c r="N2" s="3">
-        <v>9.3127682261217671E-4</v>
-      </c>
-      <c r="O2" s="3">
-        <v>3.7910533017657755E-3</v>
-      </c>
-      <c r="P2" s="3">
-        <v>4.5410392935162818E-3</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>3.8073591590627293E-3</v>
-      </c>
-      <c r="R2" s="3">
-        <v>2.4385762183190955E-3</v>
-      </c>
-      <c r="S2" s="3">
-        <v>2.9426968152120726E-3</v>
-      </c>
-      <c r="T2" s="3">
-        <v>2.4362204696603252E-3</v>
-      </c>
-      <c r="U2" s="3">
-        <v>3.8475143461624624E-2</v>
-      </c>
-      <c r="V2" s="3">
-        <v>4.6086700548772216E-2</v>
-      </c>
-      <c r="W2" s="3">
-        <v>3.864063050409719E-2</v>
-      </c>
-      <c r="X2" s="3">
-        <v>2.4748945048657631E-2</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>2.9865230878345892E-2</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>2.472503671490682E-2</v>
+      <c r="C2" s="6">
+        <v>1.504173599723199E-2</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2.9357058471310291E-2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>5.9394687751976739E-2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>9.6942951817503044E-3</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1.8176681218554019E-2</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4.3627118360180198E-2</v>
+      </c>
+      <c r="I2" s="6">
+        <v>2.358468137844755E-3</v>
+      </c>
+      <c r="J2" s="6">
+        <v>2.8250450821862118E-3</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2.368612243409611E-3</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1.517072922697429E-3</v>
+      </c>
+      <c r="M2" s="6">
+        <v>1.8306935106352409E-3</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1.5156073779766801E-3</v>
+      </c>
+      <c r="O2" s="6">
+        <v>6.169753412677636E-3</v>
+      </c>
+      <c r="P2" s="6">
+        <v>7.39031885023238E-3</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>6.1962903961216963E-3</v>
+      </c>
+      <c r="R2" s="6">
+        <v>3.9686632572644102E-3</v>
+      </c>
+      <c r="S2" s="6">
+        <v>4.7890948169137656E-3</v>
+      </c>
+      <c r="T2" s="6">
+        <v>3.964829391800137E-3</v>
+      </c>
+      <c r="U2" s="6">
+        <v>6.2616409947349877E-2</v>
+      </c>
+      <c r="V2" s="6">
+        <v>7.5003845991139101E-2</v>
+      </c>
+      <c r="W2" s="6">
+        <v>6.288573199686405E-2</v>
+      </c>
+      <c r="X2" s="6">
+        <v>4.0277694883109477E-2</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>4.8604199272602143E-2</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>4.0238785241907167E-2</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
@@ -1427,77 +1448,77 @@
       <c r="B3">
         <v>1990</v>
       </c>
-      <c r="C3" s="3">
-        <v>9.8255073386452202E-3</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1.9176509513528013E-2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3.8797578982305021E-2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>6.3324717618238316E-3</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1.1873304699536191E-2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2.8497945429355818E-2</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1.9788203893988383E-3</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2.0019962640333297E-3</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1.4685437777775861E-3</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1.2820577504743527E-3</v>
-      </c>
-      <c r="M3" s="3">
-        <v>1.2955733546455572E-3</v>
-      </c>
-      <c r="N3" s="3">
-        <v>9.6418318282022063E-4</v>
-      </c>
-      <c r="O3" s="3">
-        <v>5.3296615971374977E-3</v>
-      </c>
-      <c r="P3" s="3">
-        <v>5.3920824058583169E-3</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>3.9553066150254312E-3</v>
-      </c>
-      <c r="R3" s="3">
-        <v>3.4530339360872861E-3</v>
-      </c>
-      <c r="S3" s="3">
-        <v>3.489436227522773E-3</v>
-      </c>
-      <c r="T3" s="3">
-        <v>2.5968855534401897E-3</v>
-      </c>
-      <c r="U3" s="3">
-        <v>4.1733028382046462E-2</v>
-      </c>
-      <c r="V3" s="3">
-        <v>4.2221804139099296E-2</v>
-      </c>
-      <c r="W3" s="3">
-        <v>3.0971370361151652E-2</v>
-      </c>
-      <c r="X3" s="3">
-        <v>2.7038407717348851E-2</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>2.7323449803785382E-2</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>2.0334480253840763E-2</v>
+      <c r="C3" s="6">
+        <v>1.382232388317887E-2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2.6977123552929239E-2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>5.4579645009005362E-2</v>
+      </c>
+      <c r="F3" s="6">
+        <v>8.9083924784979333E-3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1.670312356036447E-2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>4.009033001078869E-2</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2.783764276611925E-3</v>
+      </c>
+      <c r="J3" s="6">
+        <v>2.8163676256740058E-3</v>
+      </c>
+      <c r="K3" s="6">
+        <v>2.0659175178905031E-3</v>
+      </c>
+      <c r="L3" s="6">
+        <v>1.803572767616462E-3</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1.822586244670869E-3</v>
+      </c>
+      <c r="N3" s="6">
+        <v>1.356393291086073E-3</v>
+      </c>
+      <c r="O3" s="6">
+        <v>7.4976595349561404E-3</v>
+      </c>
+      <c r="P3" s="6">
+        <v>7.5854718590888191E-3</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>5.5642448991035723E-3</v>
+      </c>
+      <c r="R3" s="6">
+        <v>4.8576579100888936E-3</v>
+      </c>
+      <c r="S3" s="6">
+        <v>4.9088679132947488E-3</v>
+      </c>
+      <c r="T3" s="6">
+        <v>3.6532457785684019E-3</v>
+      </c>
+      <c r="U3" s="6">
+        <v>5.8709175520506043E-2</v>
+      </c>
+      <c r="V3" s="6">
+        <v>5.9396775314326133E-2</v>
+      </c>
+      <c r="W3" s="6">
+        <v>4.3569893897891308E-2</v>
+      </c>
+      <c r="X3" s="6">
+        <v>3.8037082043050077E-2</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>3.8438073452782828E-2</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>2.860613323845395E-2</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
@@ -1507,77 +1528,77 @@
       <c r="B4">
         <v>2005</v>
       </c>
-      <c r="C4" s="3">
-        <v>4.3979404012379876E-3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1.8934595710058313E-2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4.6767349621220075E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2.7344871436002895E-3</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1.1999719743461217E-2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>3.2708950241670628E-2</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1.2396408709914293E-3</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2.4635173490725249E-3</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1.7826315483355124E-3</v>
-      </c>
-      <c r="L4" s="3">
-        <v>7.7551183387535494E-4</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1.5986574679063698E-3</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1.2179893011831401E-3</v>
-      </c>
-      <c r="O4" s="3">
-        <v>3.4106297461870614E-3</v>
-      </c>
-      <c r="P4" s="3">
-        <v>6.7778868441751607E-3</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>4.9045625451039458E-3</v>
-      </c>
-      <c r="R4" s="3">
-        <v>2.1336693481394994E-3</v>
-      </c>
-      <c r="S4" s="3">
-        <v>4.3983937942001341E-3</v>
-      </c>
-      <c r="T4" s="3">
-        <v>3.3510596805593137E-3</v>
-      </c>
-      <c r="U4" s="3">
-        <v>2.0884530399616071E-2</v>
-      </c>
-      <c r="V4" s="3">
-        <v>4.150347424858538E-2</v>
-      </c>
-      <c r="W4" s="3">
-        <v>3.0032426030575005E-2</v>
-      </c>
-      <c r="X4" s="3">
-        <v>1.3065235947632639E-2</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>2.6932970078956568E-2</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>2.0519761151971804E-2</v>
+      <c r="C4" s="6">
+        <v>5.7941119571865551E-3</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2.4945578475156192E-2</v>
+      </c>
+      <c r="E4" s="6">
+        <v>6.1614127278750243E-2</v>
+      </c>
+      <c r="F4" s="6">
+        <v>3.602578300298794E-3</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1.5809154582655249E-2</v>
+      </c>
+      <c r="H4" s="6">
+        <v>4.3092743969185117E-2</v>
+      </c>
+      <c r="I4" s="6">
+        <v>1.633177655433153E-3</v>
+      </c>
+      <c r="J4" s="6">
+        <v>3.2455863487780888E-3</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2.3485463255848819E-3</v>
+      </c>
+      <c r="L4" s="6">
+        <v>1.0217060668516579E-3</v>
+      </c>
+      <c r="M4" s="6">
+        <v>2.1061677751782332E-3</v>
+      </c>
+      <c r="N4" s="6">
+        <v>1.60465257140001E-3</v>
+      </c>
+      <c r="O4" s="6">
+        <v>4.4933693481512072E-3</v>
+      </c>
+      <c r="P4" s="6">
+        <v>8.9295969534371172E-3</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>6.4615665276766274E-3</v>
+      </c>
+      <c r="R4" s="6">
+        <v>2.8110246967552139E-3</v>
+      </c>
+      <c r="S4" s="6">
+        <v>5.7947092844223983E-3</v>
+      </c>
+      <c r="T4" s="6">
+        <v>4.4148881505781433E-3</v>
+      </c>
+      <c r="U4" s="6">
+        <v>2.751454005028783E-2</v>
+      </c>
+      <c r="V4" s="6">
+        <v>5.4679180359247397E-2</v>
+      </c>
+      <c r="W4" s="6">
+        <v>3.9566529532344838E-2</v>
+      </c>
+      <c r="X4" s="6">
+        <v>1.7212929899262049E-2</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>3.5483119310371347E-2</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>2.7033971041486662E-2</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.35">
@@ -1587,77 +1608,77 @@
       <c r="B5">
         <v>2024</v>
       </c>
-      <c r="C5" s="3">
-        <v>1.5116042286348469E-3</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2.1252206081061563E-2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>5.5338632537204356E-2</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="C5" s="6">
+        <v>1.5116042286348471E-3</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2.1252206081061559E-2</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5.5338632537204363E-2</v>
+      </c>
+      <c r="F5" s="6">
         <v>9.5153869066014923E-4</v>
       </c>
-      <c r="G5" s="3">
-        <v>1.4018091807244585E-2</v>
-      </c>
-      <c r="H5" s="3">
-        <v>3.7341383411790365E-2</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="G5" s="6">
+        <v>1.4018091807244591E-2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3.7341383411790358E-2</v>
+      </c>
+      <c r="I5" s="6">
         <v>4.8269051570177472E-4</v>
       </c>
-      <c r="J5" s="3">
-        <v>3.7406532133700265E-3</v>
-      </c>
-      <c r="K5" s="3">
-        <v>3.3895711962685687E-3</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="J5" s="6">
+        <v>3.740653213370027E-3</v>
+      </c>
+      <c r="K5" s="6">
+        <v>3.3895711962685692E-3</v>
+      </c>
+      <c r="L5" s="6">
         <v>3.023578733477638E-4</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="6">
         <v>2.4747087023300062E-3</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="6">
         <v>2.3138745106789358E-3</v>
       </c>
-      <c r="O5" s="3">
-        <v>1.0564083484407927E-3</v>
-      </c>
-      <c r="P5" s="3">
-        <v>6.9575854914156205E-3</v>
-      </c>
-      <c r="Q5" s="3">
+      <c r="O5" s="6">
+        <v>1.0564083484407929E-3</v>
+      </c>
+      <c r="P5" s="6">
+        <v>6.9575854914156214E-3</v>
+      </c>
+      <c r="Q5" s="6">
         <v>6.0718239271718216E-3</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="6">
         <v>6.6021946788870042E-4</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="6">
         <v>4.5447953716199543E-3</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="6">
         <v>4.2407007135885728E-3</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="6">
         <v>6.7774666058225529E-3</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="6">
         <v>4.4602112830308398E-2</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="6">
         <v>3.9108563794420327E-2</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="6">
         <v>4.2348582992285388E-3</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="6">
         <v>2.9149210218059302E-2</v>
       </c>
-      <c r="Z5" s="3">
-        <v>2.7321796414283506E-2</v>
+      <c r="Z5" s="6">
+        <v>2.7321796414283509E-2</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
@@ -1990,73 +2011,73 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>14.298647537812691</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>8.0259221354587336</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>4.3760853001769764</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>3.5876780420171328</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>44.622929584946398</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>25.04713521735102</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>13.656798357405199</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>11.196352957090847</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <v>15.801499760938905</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>8.8694826814484671</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="5">
         <v>4.8360315646449346</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="5">
         <v>3.9647591545522936</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="5">
         <v>143.25371296273633</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="5">
         <v>80.409223516684932</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Y10" s="5">
         <v>43.842640769638827</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="Z10" s="5">
         <v>35.943833084541822</v>
       </c>
     </row>
@@ -2070,73 +2091,73 @@
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>10.894129101927685</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>7.1082859227863864</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>3.5992004691417323</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>3.0507476594685032</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>33.998177416365564</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>22.183394713615311</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>11.232311914248786</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <v>9.520711495957876</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <v>12.039151111635922</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="5">
         <v>7.8553987719860006</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="S11" s="6">
+      <c r="S11" s="5">
         <v>3.9774926406371356</v>
       </c>
-      <c r="T11" s="6">
+      <c r="T11" s="5">
         <v>3.3713949717478497</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" s="6">
+      <c r="V11" s="5">
         <v>109.14489913955002</v>
       </c>
-      <c r="W11" s="6">
+      <c r="W11" s="5">
         <v>71.215711034700504</v>
       </c>
       <c r="X11">
         <v>0</v>
       </c>
-      <c r="Y11" s="6">
+      <c r="Y11" s="5">
         <v>36.059272706616312</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="Z11" s="5">
         <v>30.564494185587478</v>
       </c>
     </row>
@@ -2150,73 +2171,73 @@
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>9.9268837871518212</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>8.2132911048255579</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>3.7188048169150183</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>3.5818618984539139</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>30.979617831728419</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>25.631872501373813</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>11.605570739926311</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <v>11.178202054077738</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <v>10.97024396011814</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="5">
         <v>9.0765449729573451</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="5">
         <v>4.1096679437732488</v>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="5">
         <v>3.9583317081185836</v>
       </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" s="6">
+      <c r="V12" s="5">
         <v>99.454368456768421</v>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="5">
         <v>82.286415082168119</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
-      <c r="Y12" s="6">
+      <c r="Y12" s="5">
         <v>37.257551554996866</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="Z12" s="5">
         <v>35.885562946869562</v>
       </c>
     </row>
@@ -2230,73 +2251,73 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>10.379478235753581</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>9.3649135884610573</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>4.2050907058008926</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>4.3774729044004834</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>32.392065418612816</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>29.225832619616511</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>13.123161891153952</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="5">
         <v>13.661128764556896</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="5">
         <v>11.470408122670609</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="5">
         <v>10.349208163775593</v>
       </c>
       <c r="R13">
         <v>0</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="5">
         <v>4.6470646686493389</v>
       </c>
-      <c r="T13" s="6">
+      <c r="T13" s="5">
         <v>4.8375650123187821</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" s="6">
+      <c r="V13" s="5">
         <v>103.98877180205452</v>
       </c>
-      <c r="W13" s="6">
+      <c r="W13" s="5">
         <v>93.82416340947529</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
-      <c r="Y13" s="6">
+      <c r="Y13" s="5">
         <v>42.129498986393067</v>
       </c>
-      <c r="Z13" s="6">
+      <c r="Z13" s="5">
         <v>43.856542745795281</v>
       </c>
     </row>
